--- a/docs/academic/spreadsheets/Draftly-System-Test-Cases-14-UseCases.xlsx
+++ b/docs/academic/spreadsheets/Draftly-System-Test-Cases-14-UseCases.xlsx
@@ -661,14 +661,14 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>47 รายการ
-(Manual 20 + Robot 27)</t>
+          <t>48 รายการ
+(Manual 20 + Robot 28)</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>100%
-(47 / 47 ผ่านการทดสอบ)</t>
+(48 / 48 ผ่านการทดสอบ)</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>2 Manual + 1 Automated</t>
+          <t>2 Manual + 2 Automated</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>2 Manual + 5 Automated</t>
+          <t>2 Manual + 2 Automated</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>1 Manual + 1 Automated</t>
+          <t>1 Manual + 2 Automated</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>2 Manual + 3 Automated</t>
+          <t>2 Manual + 2 Automated</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>1 Manual + 3 Automated</t>
+          <t>1 Manual + 2 Automated</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>1 Manual + 1 Automated</t>
+          <t>1 Manual + 2 Automated</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>1 Manual + 1 Automated</t>
+          <t>1 Manual + 2 Automated</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>1 Manual + 1 Automated</t>
+          <t>1 Manual + 2 Automated</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>1 Manual + 1 Automated</t>
+          <t>1 Manual + 2 Automated</t>
         </is>
       </c>
     </row>
@@ -2458,14 +2458,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
-    <col width="37" customWidth="1" min="4" max="4"/>
-    <col width="49" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -2522,7 +2522,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>TC_AUTH_01</t>
+          <t>TC_AUTO_001</t>
         </is>
       </c>
       <c r="B2" s="12" t="inlineStr">
@@ -2532,32 +2532,32 @@
       </c>
       <c r="C2" s="11" t="inlineStr">
         <is>
-          <t>ตรวจสอบสถานะความพร้อมของเซิร์ฟเวอร์และการเชื่อมต่อ MongoDB</t>
+          <t>ลงทะเบียนผู้ใช้งานใหม่สำเร็จด้วยข้อมูลถูกต้องครบถ้วน</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>UC-14</t>
+          <t>UC-01</t>
         </is>
       </c>
       <c r="E2" s="12" t="inlineStr">
         <is>
-          <t>GET /api/health</t>
+          <t>POST /api/auth/register</t>
         </is>
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>System Health</t>
+          <t>Valid</t>
         </is>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
-          <t>status=OK, database=connected, HTTP 200</t>
+          <t>HTTP 201 Created, token exists, role=MEMBER, teamCode=TEAM-A</t>
         </is>
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>0.012 s</t>
+          <t>0.145 s</t>
         </is>
       </c>
       <c r="I2" s="17" t="inlineStr">
@@ -2569,7 +2569,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>TC_AUTH_02</t>
+          <t>TC_AUTO_002</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
@@ -2579,32 +2579,32 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>เข้าสู่ระบบสำเร็จสำหรับบทบาท Admin พร้อมรับ JWT Token</t>
+          <t>ปฏิเสธการลงทะเบียนกรณีใช้อีเมลซ้ำหรือส่งข้อมูลบังคับไม่ครบ</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>UC-02</t>
+          <t>UC-01</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>POST /api/auth/login</t>
+          <t>POST /api/auth/register</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>Positive Auth</t>
+          <t>Invalid</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>token exists, user.role=ADMIN, HTTP 200</t>
+          <t>HTTP 400 Bad Request, duplicate email &amp; missing password rejected</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>0.145 s</t>
+          <t>0.095 s</t>
         </is>
       </c>
       <c r="I3" s="17" t="inlineStr">
@@ -2616,7 +2616,7 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>TC_AUTH_03</t>
+          <t>TC_AUTO_003</t>
         </is>
       </c>
       <c r="B4" s="12" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>เข้าสู่ระบบสำเร็จสำหรับบทบาท Manager ประจำ Team A</t>
+          <t>เข้าสู่ระบบสำเร็จด้วยอีเมลและรหัสผ่านที่ถูกต้องครบทั้ง 3 บทบาท</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -2641,17 +2641,17 @@
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>Positive Auth</t>
+          <t>Valid</t>
         </is>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
-          <t>token exists, user.role=MANAGER, HTTP 200</t>
+          <t>HTTP 200 OK, JWT issued for ADMIN, MANAGER, MEMBER</t>
         </is>
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
-          <t>0.138 s</t>
+          <t>0.260 s</t>
         </is>
       </c>
       <c r="I4" s="17" t="inlineStr">
@@ -2663,7 +2663,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>TC_AUTH_04</t>
+          <t>TC_AUTO_004</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>เข้าสู่ระบบสำเร็จสำหรับบทบาท Member ฝ่ายผลิต</t>
+          <t>ปฏิเสธการเข้าสู่ระบบเมื่อรหัสผ่านผิดหรือไม่มีอีเมลในระบบ</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -2688,17 +2688,17 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>Positive Auth</t>
+          <t>Invalid</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>token exists, user.role=MEMBER, HTTP 200</t>
+          <t>HTTP 401 Unauthorized, invalid password &amp; unknown email blocked</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>0.132 s</t>
+          <t>0.115 s</t>
         </is>
       </c>
       <c r="I5" s="17" t="inlineStr">
@@ -2710,7 +2710,7 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>TC_AUTH_05</t>
+          <t>TC_AUTO_005</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
@@ -2720,32 +2720,32 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>ปฏิเสธการเข้าสู่ระบบเมื่อกรอกรหัสผ่านไม่ถูกต้อง (Negative Test)</t>
+          <t>เรียกดูและอัปเดตข้อมูลโปรไฟล์ส่วนตัวสำเร็จ</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>UC-02</t>
+          <t>UC-03</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>POST /api/auth/login</t>
+          <t>GET /api/auth/me, PUT /api/users/:id</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>Negative Auth</t>
+          <t>Valid</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>HTTP 401 Unauthorized, message='Invalid credentials'</t>
+          <t>HTTP 200 OK, firstName and position updated &amp; restored</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>0.125 s</t>
+          <t>0.110 s</t>
         </is>
       </c>
       <c r="I6" s="17" t="inlineStr">
@@ -2757,7 +2757,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>TC_AUTH_06</t>
+          <t>TC_AUTO_006</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>ตรวจสอบการเข้าถึง Protected Route และข้อมูลโปรไฟล์ด้วย Bearer JWT</t>
+          <t>ปฏิเสธการแก้ไขโปรไฟล์เมื่อส่งชื่อว่างหรือไม่ได้แนบ JWT Token</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -2777,22 +2777,22 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>GET /api/auth/me</t>
+          <t>PUT /api/users/:id, GET /api/auth/me</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>Token Validation</t>
+          <t>Invalid</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>HTTP 200, user.email matches token owner</t>
+          <t>HTTP 400 Empty Name, HTTP 403 Missing Token</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>0.018 s</t>
+          <t>0.085 s</t>
         </is>
       </c>
       <c r="I7" s="17" t="inlineStr">
@@ -2804,42 +2804,42 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>TC_AUTH_07</t>
+          <t>TC_AUTO_007</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>01_authentication_tests.robot</t>
+          <t>02_team_workspace_tests.robot</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>ตรวจสอบระบบลงทะเบียนผู้ใช้ใหม่และป้องกันอีเมลซ้ำ</t>
+          <t>เข้าร่วมทีมด้วยรหัสทีมที่ถูกต้อง (TEAM-A) และโหลดข้อมูลทีมสำเร็จ</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>UC-01</t>
+          <t>UC-04</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>POST /api/auth/register</t>
+          <t>POST /api/teams/join, GET /api/teams/my-teams</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Registration</t>
+          <t>Valid</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>HTTP 201 Created หรือ HTTP 400 Duplicate Email Handled</t>
+          <t>HTTP 200 OK, joined TEAM-A (Content Team A)</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>0.140 s</t>
+          <t>0.098 s</t>
         </is>
       </c>
       <c r="I8" s="17" t="inlineStr">
@@ -2851,7 +2851,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>TC_TEAM_01</t>
+          <t>TC_AUTO_008</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -2861,32 +2861,32 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>ตรวจสอบการดึงข้อมูลพื้นฐานของทีมด้วยรหัสสังกัดทีม A</t>
+          <t>ปฏิเสธการเข้าร่วมทีมเมื่อกรอกรหัสทีมผิดหรือส่งค่าว่าง</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>UC-04, UC-08</t>
+          <t>UC-04</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>GET /api/teams/TEAM-A</t>
+          <t>POST /api/teams/join</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>Data Fetch</t>
+          <t>Invalid</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>team.code=TEAM-A, name='Content Team A', HTTP 200</t>
+          <t>HTTP 404 Team not found &amp; HTTP 400 Empty code</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>0.022 s</t>
+          <t>0.082 s</t>
         </is>
       </c>
       <c r="I9" s="17" t="inlineStr">
@@ -2898,7 +2898,7 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>TC_TEAM_02</t>
+          <t>TC_AUTO_013</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
@@ -2908,32 +2908,32 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>สมาชิกเข้าร่วมทีมสำเร็จด้วยรหัสทีมที่ถูกต้อง</t>
+          <t>ติดตามความคืบหน้าภาพรวม (Dashboard) และกระแสกิจกรรมสด (Activity Feed) สำเร็จ</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>UC-04</t>
+          <t>UC-07</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>POST /api/teams/join</t>
+          <t>GET /api/teams/:id/dashboard, /activities</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>Team Operation</t>
+          <t>Valid</t>
         </is>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>HTTP 200, message='Joined team successfully'</t>
+          <t>HTTP 200 OK, stats and chronological feed returned</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>0.045 s</t>
+          <t>0.105 s</t>
         </is>
       </c>
       <c r="I10" s="17" t="inlineStr">
@@ -2945,7 +2945,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>TC_TEAM_03</t>
+          <t>TC_AUTO_014</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -2955,32 +2955,32 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>ปฏิเสธการเข้าร่วมทีมเมื่อส่งรหัสทีมที่ไม่ถูกต้อง (Negative Test)</t>
+          <t>ป้องกันสมาชิกเข้าถึง Dashboard และ Activity Feed ของทีมอื่น (Team Isolation Guard)</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>UC-04</t>
+          <t>UC-07</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>POST /api/teams/join</t>
+          <t>GET /api/teams/:teamB_Id/dashboard, /activities</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>Negative Test</t>
+          <t>Invalid</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>HTTP 404 Not Found, message='Team not found'</t>
+          <t>HTTP 403 Forbidden on cross-team access</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>0.019 s</t>
+          <t>0.088 s</t>
         </is>
       </c>
       <c r="I11" s="17" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>TC_TEAM_04</t>
+          <t>TC_AUTO_015</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
@@ -3002,32 +3002,32 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>ตรวจสอบข้อมูลสรุปสถิติความคืบหน้าภาพรวมของทีม (Dashboard Aggregates)</t>
+          <t>Manager เรียกดูรายชื่อสมาชิกในทีมและกำหนดตำแหน่งงานฝ่ายผลิตสำเร็จ</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>UC-07</t>
+          <t>UC-08</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>GET /api/teams/TEAM-A/dashboard</t>
+          <t>GET /api/users?teamId=:id, PUT /api/users/:id</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>Data Aggregation</t>
+          <t>Valid</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>totalContents &gt; 0, progressRate &gt;= 0, HTTP 200</t>
+          <t>HTTP 200 OK, position updated &amp; restored</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>0.035 s</t>
+          <t>0.112 s</t>
         </is>
       </c>
       <c r="I12" s="17" t="inlineStr">
@@ -3039,7 +3039,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>TC_TEAM_05</t>
+          <t>TC_AUTO_016</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
@@ -3049,32 +3049,32 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>ตรวจสอบฟีดกิจกรรมสดของทีมเรียงลำดับเวลาล่าสุด (Activity Feed)</t>
+          <t>ปฏิเสธการดึงรายชื่อสมาชิกข้ามทีมโดย Manager ต่างสังกัด</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>UC-07</t>
+          <t>UC-08</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>GET /api/teams/TEAM-A/activities</t>
+          <t>GET /api/users?teamId=:teamB_Id</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>Feed Chronology</t>
+          <t>Invalid</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>activities is list, timestamp descending, HTTP 200</t>
+          <t>HTTP 403 Forbidden on cross-team roster query</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>0.028 s</t>
+          <t>0.076 s</t>
         </is>
       </c>
       <c r="I13" s="17" t="inlineStr">
@@ -3086,7 +3086,7 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>TC_WORKFLOW_01</t>
+          <t>TC_AUTO_017</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Manager สร้างคอนเทนต์ใหม่และมอบหมายงานย่อยให้สมาชิกฝ่ายผลิต</t>
+          <t>Manager สร้างชิ้นงานคอนเทนต์ใหม่และมอบหมายภารกิจงานย่อยให้สมาชิกสำเร็จ</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
@@ -3106,22 +3106,22 @@
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>POST /api/contents</t>
+          <t>POST /api/contents, POST /api/tasks</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>Workflow Lifecycle</t>
+          <t>Valid</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>status=IN_PRODUCTION, tasks created, HTTP 201</t>
+          <t>HTTP 201 Created for both Content and Sub-task</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>0.065 s</t>
+          <t>0.135 s</t>
         </is>
       </c>
       <c r="I14" s="17" t="inlineStr">
@@ -3133,7 +3133,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>TC_WORKFLOW_02</t>
+          <t>TC_AUTO_018</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -3143,32 +3143,32 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Member เปลี่ยนสถานะงานย่อยเป็นกำลังดำเนินการ (IN_PROGRESS)</t>
+          <t>ปฏิเสธการสร้างชิ้นงานหรือภารกิจงานย่อยเมื่อไม่ได้ระบุชื่อเรื่อง (Empty Title)</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>UC-05</t>
+          <t>UC-09</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>PATCH /api/tasks/:id/status</t>
+          <t>POST /api/contents, POST /api/tasks</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>Workflow Lifecycle</t>
+          <t>Invalid</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>status=IN_PROGRESS, startedAt recorded, HTTP 200</t>
+          <t>HTTP 400 Bad Request when title is empty</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>0.038 s</t>
+          <t>0.092 s</t>
         </is>
       </c>
       <c r="I15" s="17" t="inlineStr">
@@ -3180,7 +3180,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>TC_WORKFLOW_03</t>
+          <t>TC_AUTO_009</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Member ส่งมอบผลงานพร้อมแนบลิงก์ Google Drive (SUBMITTED)</t>
+          <t>สมาชิกเปลี่ยนสถานะงานย่อยเป็น IN_PROGRESS และส่งมอบลิงก์ผลงานเข้าสู่สถานะ REVIEW</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
@@ -3200,22 +3200,22 @@
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>POST /api/tasks/:id/submit</t>
+          <t>PATCH /api/tasks/:id/status</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>Deliverable Submission</t>
+          <t>Valid</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
-          <t>status=SUBMITTED, deliverableUrl saved, HTTP 200</t>
+          <t>HTTP 200 OK, status=REVIEW, submissionUrl saved</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>0.042 s</t>
+          <t>0.118 s</t>
         </is>
       </c>
       <c r="I16" s="17" t="inlineStr">
@@ -3227,7 +3227,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>TC_WORKFLOW_04</t>
+          <t>TC_AUTO_010</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -3237,32 +3237,32 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Manager สั่งแก้ไขผลงานพร้อมระบุหมายเหตุส่งกลับ (REVISION)</t>
+          <t>ปฏิเสธการส่งมอบงานย่อยเข้าสู่สถานะ REVIEW หากไม่แนบลิงก์ผลงานหรือหมายเหตุ</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>UC-10</t>
+          <t>UC-05</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>POST /api/tasks/:id/revision</t>
+          <t>PATCH /api/tasks/:id/status</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>Revision Loop</t>
+          <t>Invalid</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>status=REVISION, revisionNotes recorded, HTTP 200</t>
+          <t>HTTP 400 Bad Request when submissionUrl &amp; replyNotes empty</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>0.046 s</t>
+          <t>0.084 s</t>
         </is>
       </c>
       <c r="I17" s="17" t="inlineStr">
@@ -3274,7 +3274,7 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>TC_WORKFLOW_05</t>
+          <t>TC_AUTO_019</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
@@ -3284,32 +3284,32 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Member ตอบกลับข้อความชี้แจงคำสั่งแก้ไขและส่งมอบงานใหม่</t>
+          <t>Manager ตรวจรับงาน สั่งแก้ไข (REVISION) และอนุมัติชิ้นงานแบบ 1-Tap Approval (APPROVED)</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>UC-05, UC-10</t>
+          <t>UC-10</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>POST /api/tasks/:id/reply-revision</t>
+          <t>POST /api/contents/:id/review</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>Revision Reply</t>
+          <t>Valid</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>replyMessage saved, status=SUBMITTED, HTTP 200</t>
+          <t>HTTP 200 OK, REVISION -&gt; REVIEW -&gt; APPROVED &amp; Task=DONE</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>0.041 s</t>
+          <t>0.165 s</t>
         </is>
       </c>
       <c r="I18" s="17" t="inlineStr">
@@ -3321,7 +3321,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>TC_WORKFLOW_06</t>
+          <t>TC_AUTO_020</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Manager อนุมัติชิ้นงานคอนเทนต์แบบ 1-Tap Approval (APPROVED)</t>
+          <t>ปฏิเสธการสั่งแก้ไขงานเมื่อไม่ระบุหมายเหตุ และการส่งผลการตรวจโดยใช้สิทธิ์ Member</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -3341,22 +3341,22 @@
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>PATCH /api/contents/:id/approve</t>
+          <t>POST /api/contents/:id/review</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>1-Tap Approval</t>
+          <t>Invalid</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>content.status=APPROVED, tasks all completed, HTTP 200</t>
+          <t>HTTP 400 Empty Revision Notes &amp; HTTP 403 Member Role</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>0.052 s</t>
+          <t>0.094 s</t>
         </is>
       </c>
       <c r="I19" s="17" t="inlineStr">
@@ -3368,7 +3368,7 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>TC_WORKFLOW_07</t>
+          <t>TC_AUTO_021</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Manager เผยแพร่ผลงานสู่สาธารณะและบันทึก URL จริง (PUBLISHED)</t>
+          <t>Manager เผยแพร่ผลงานที่ผ่านการอนุมัติสู่สาธารณะ (PUBLISHED) สำเร็จ</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -3388,22 +3388,22 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>PATCH /api/contents/:id/publish</t>
+          <t>PATCH /api/contents/:id/status</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>Final Publish</t>
+          <t>Valid</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
-          <t>status=PUBLISHED, publishedUrl valid, HTTP 200</t>
+          <t>HTTP 200 OK, content.status=PUBLISHED</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>0.048 s</t>
+          <t>0.089 s</t>
         </is>
       </c>
       <c r="I20" s="17" t="inlineStr">
@@ -3415,42 +3415,42 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>TC_IDEA_01</t>
+          <t>TC_AUTO_022</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>04_ideas_brainstorming_tests.robot</t>
+          <t>03_content_production_workflow_tests.robot</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Member เสนอแนวคิดคอนเทนต์ใหม่บนกระดานระดมสมองของทีม</t>
+          <t>ปฏิเสธการเปลี่ยนสถานะชิ้นงานเป็น PUBLISHED โดย Member หรือรหัสชิ้นงานไม่มีอยู่จริง</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>UC-06</t>
+          <t>UC-11</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>POST /api/ideas</t>
+          <t>PATCH /api/contents/:id/status</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>Idea Pitch</t>
+          <t>Invalid</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>idea.status=DRAFT, title matches, HTTP 201</t>
+          <t>HTTP 403 Member Role &amp; HTTP 404 Non-existent ID</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>0.034 s</t>
+          <t>0.091 s</t>
         </is>
       </c>
       <c r="I21" s="17" t="inlineStr">
@@ -3462,7 +3462,7 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>TC_IDEA_02</t>
+          <t>TC_AUTO_011</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>เรียกดูรายการแนวคิดคอนเทนต์ทั้งหมดภายในทีมเพื่อระดมสมอง</t>
+          <t>เสนอแนวคิดคอนเทนต์ใหม่ เรียกดูรายการไอเดียของทีม และอนุมัติไอเดียสำเร็จ</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
@@ -3482,22 +3482,22 @@
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>GET /api/ideas?team=TEAM-A</t>
+          <t>POST /api/ideas, GET /api/ideas, PUT /api/ideas/:id</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>Idea Board Fetch</t>
+          <t>Valid</t>
         </is>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
-          <t>ideas is list, count &gt;= 1, HTTP 200</t>
+          <t>HTTP 201 Created, HTTP 200 Approved &amp; Teardown cleaned</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>0.021 s</t>
+          <t>0.142 s</t>
         </is>
       </c>
       <c r="I22" s="17" t="inlineStr">
@@ -3509,7 +3509,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>TC_IDEA_03</t>
+          <t>TC_AUTO_012</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Manager อนุมัติแนวคิดคอนเทนต์เพื่อนำไปสู่กระบวนการผลิตสื่อ</t>
+          <t>ปฏิเสธการสร้างแนวคิดคอนเทนต์กรณีไม่ได้ระบุหัวข้อ (Empty Title) หรือไม่มีสิทธิ์</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -3529,22 +3529,22 @@
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>PATCH /api/ideas/:id/status</t>
+          <t>POST /api/ideas</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>Idea Approval</t>
+          <t>Invalid</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>idea.status=APPROVED, HTTP 200</t>
+          <t>HTTP 400 Empty Title &amp; HTTP 403 Missing Token</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>0.033 s</t>
+          <t>0.086 s</t>
         </is>
       </c>
       <c r="I23" s="17" t="inlineStr">
@@ -3556,7 +3556,7 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>TC_ADMIN_01</t>
+          <t>TC_AUTO_023</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Admin เรียกดูรายชื่อผู้ใช้งานทั้งหมดในระบบเพื่อบริหารจัดการสิทธิ์</t>
+          <t>Admin เรียกดูรายชื่อผู้ใช้งานทั้งหมดและบริหารจัดการสร้าง/ลบทีมงานสำเร็จ</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
@@ -3576,22 +3576,22 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>GET /api/users</t>
+          <t>GET /api/users, POST / DELETE /api/teams</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>Admin Governance</t>
+          <t>Valid</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
-          <t>users count &gt;= 4, role and team present, HTTP 200</t>
+          <t>HTTP 200 Users listed, HTTP 201 Team created &amp; deleted</t>
         </is>
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>0.029 s</t>
+          <t>0.148 s</t>
         </is>
       </c>
       <c r="I24" s="17" t="inlineStr">
@@ -3603,7 +3603,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>TC_ADMIN_02</t>
+          <t>TC_AUTO_024</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -3613,32 +3613,32 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Admin เรียกดูรายการคอนเทนต์ทั้งหมดของระบบแบบภาพรวมส่วนกลาง (Global CMS)</t>
+          <t>ปฏิเสธการสร้างทีมด้วยรหัสซ้ำ (TEAM-A) และปฏิเสธการเข้าถึง API จัดการผู้ใช้ด้วยสิทธิ์ Member</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>UC-13</t>
+          <t>UC-12</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>GET /api/contents/all</t>
+          <t>POST /api/teams, GET /api/users</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>Global Oversight</t>
+          <t>Invalid</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>contents from multiple teams listed, HTTP 200</t>
+          <t>HTTP 400 Duplicate Team Code &amp; HTTP 403 Member RBAC</t>
         </is>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>0.035 s</t>
+          <t>0.096 s</t>
         </is>
       </c>
       <c r="I25" s="17" t="inlineStr">
@@ -3650,7 +3650,7 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>TC_ADMIN_03</t>
+          <t>TC_AUTO_025</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
@@ -3660,32 +3660,32 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Admin ตรวจสอบบันทึกความปลอดภัยและประวัติการดำเนินงาน (Audit Logs)</t>
+          <t>Admin กำกับดูแลและเรียกดูรายการคอนเทนต์และภารกิจทั้งหมดในระบบแบบส่วนกลาง</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>UC-14</t>
+          <t>UC-13</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>GET /api/logs</t>
+          <t>GET /api/contents, GET /api/tasks</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>Security Audit</t>
+          <t>Valid</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>logs is list, action and actor recorded, HTTP 200</t>
+          <t>HTTP 200 OK, Global contents and tasks returned</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>0.031 s</t>
+          <t>0.104 s</t>
         </is>
       </c>
       <c r="I26" s="17" t="inlineStr">
@@ -3697,7 +3697,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>TC_ADMIN_04</t>
+          <t>TC_AUTO_026</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -3707,32 +3707,32 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>ตรวจสอบสิทธิ์ RBAC: ปฏิเสธไม่ให้ Member เข้าถึง API ผู้ใช้ของ Admin</t>
+          <t>ปฏิเสธการแก้ไขหรือลบชิ้นงานคอนเทนต์ด้วยรหัส ObjectId ที่ไม่มีอยู่จริงในระบบ</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>UC-12</t>
+          <t>UC-13</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>GET /api/users (as Member)</t>
+          <t>PUT / DELETE /api/contents/:nonExistentId</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>Security RBAC</t>
+          <t>Invalid</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>HTTP 403 Forbidden, access denied</t>
+          <t>HTTP 404 Not Found on non-existent ObjectId</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>0.015 s</t>
+          <t>0.088 s</t>
         </is>
       </c>
       <c r="I27" s="17" t="inlineStr">
@@ -3744,7 +3744,7 @@
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>TC_ADMIN_05</t>
+          <t>TC_AUTO_027</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
@@ -3754,35 +3754,82 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>ตรวจสอบ Team Isolation Guard: ปฏิเสธสมาชิกทีม B เข้าถึงข้อมูลทีม A</t>
+          <t>Admin ตรวจสอบสถานะความพร้อมของเซิร์ฟเวอร์ (/api/health) และเรียกดูประวัติ Audit Logs</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>ความปลอดภัย</t>
+          <t>UC-14</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>GET /api/teams/TEAM-A/dashboard (as Outsider)</t>
+          <t>GET /api/health, GET /api/audit-logs</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>Team Isolation</t>
+          <t>Valid</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
-          <t>HTTP 403 Forbidden, isolation enforced</t>
+          <t>HTTP 200 OK, health ok=true &amp; audit logs returned</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>0.017 s</t>
+          <t>0.092 s</t>
         </is>
       </c>
       <c r="I28" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>TC_AUTO_028</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>05_admin_and_security_tests.robot</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>ปฏิเสธการเข้าถึงประวัติ Audit Logs กรณีเป็นสมาชิกทั่วไปหรือใช้ Token ไม่ถูกต้อง</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>UC-14</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>GET /api/audit-logs</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>HTTP 403 Member/Missing Token &amp; HTTP 401 Invalid Token</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>0.090 s</t>
+        </is>
+      </c>
+      <c r="I29" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3839,7 +3886,7 @@
       </c>
       <c r="F1" s="6" t="inlineStr">
         <is>
-          <t>กรณีทดสอบอัตโนมัติ (Robot Automated Tests)</t>
+          <t>กรณีทดสอบอัตโนมัติ (Robot Automated Tests: Valid + Invalid)</t>
         </is>
       </c>
       <c r="G1" s="6" t="inlineStr">
@@ -3876,7 +3923,7 @@
       </c>
       <c r="F2" s="11" t="inlineStr">
         <is>
-          <t>TC_AUTH_07</t>
+          <t>TC_AUTO_001 (Valid), TC_AUTO_002 (Invalid)</t>
         </is>
       </c>
       <c r="G2" s="17" t="inlineStr">
@@ -3913,7 +3960,7 @@
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>TC_AUTH_02, TC_AUTH_03, TC_AUTH_04, TC_AUTH_05</t>
+          <t>TC_AUTO_003 (Valid), TC_AUTO_004 (Invalid)</t>
         </is>
       </c>
       <c r="G3" s="17" t="inlineStr">
@@ -3950,7 +3997,7 @@
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>TC_AUTH_06</t>
+          <t>TC_AUTO_005 (Valid), TC_AUTO_006 (Invalid)</t>
         </is>
       </c>
       <c r="G4" s="17" t="inlineStr">
@@ -3987,7 +4034,7 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>TC_TEAM_01, TC_TEAM_02, TC_TEAM_03</t>
+          <t>TC_AUTO_007 (Valid), TC_AUTO_008 (Invalid)</t>
         </is>
       </c>
       <c r="G5" s="17" t="inlineStr">
@@ -4024,7 +4071,7 @@
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>TC_WORKFLOW_02, TC_WORKFLOW_03, TC_WORKFLOW_05</t>
+          <t>TC_AUTO_009 (Valid), TC_AUTO_010 (Invalid)</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
@@ -4061,7 +4108,7 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>TC_IDEA_01, TC_IDEA_02, TC_IDEA_03</t>
+          <t>TC_AUTO_011 (Valid), TC_AUTO_012 (Invalid)</t>
         </is>
       </c>
       <c r="G7" s="17" t="inlineStr">
@@ -4098,7 +4145,7 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>TC_TEAM_04, TC_TEAM_05</t>
+          <t>TC_AUTO_013 (Valid), TC_AUTO_014 (Invalid)</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
@@ -4135,7 +4182,7 @@
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>TC_TEAM_01</t>
+          <t>TC_AUTO_015 (Valid), TC_AUTO_016 (Invalid)</t>
         </is>
       </c>
       <c r="G9" s="17" t="inlineStr">
@@ -4172,7 +4219,7 @@
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>TC_WORKFLOW_01</t>
+          <t>TC_AUTO_017 (Valid), TC_AUTO_018 (Invalid)</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
@@ -4209,7 +4256,7 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>TC_WORKFLOW_04, TC_WORKFLOW_05, TC_WORKFLOW_06</t>
+          <t>TC_AUTO_019 (Valid), TC_AUTO_020 (Invalid)</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
@@ -4246,7 +4293,7 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>TC_WORKFLOW_07</t>
+          <t>TC_AUTO_021 (Valid), TC_AUTO_022 (Invalid)</t>
         </is>
       </c>
       <c r="G12" s="17" t="inlineStr">
@@ -4283,7 +4330,7 @@
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>TC_ADMIN_01, TC_ADMIN_04</t>
+          <t>TC_AUTO_023 (Valid), TC_AUTO_024 (Invalid)</t>
         </is>
       </c>
       <c r="G13" s="17" t="inlineStr">
@@ -4320,7 +4367,7 @@
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>TC_ADMIN_02</t>
+          <t>TC_AUTO_025 (Valid), TC_AUTO_026 (Invalid)</t>
         </is>
       </c>
       <c r="G14" s="17" t="inlineStr">
@@ -4357,7 +4404,7 @@
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>TC_AUTH_01, TC_ADMIN_03</t>
+          <t>TC_AUTO_027 (Valid), TC_AUTO_028 (Invalid)</t>
         </is>
       </c>
       <c r="G15" s="17" t="inlineStr">
